--- a/KatalonData/RADTestData/EL-NumberValidation.xlsx
+++ b/KatalonData/RADTestData/EL-NumberValidation.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="395">
   <si>
     <t>Result</t>
   </si>
@@ -862,6 +862,366 @@
   </si>
   <si>
     <t>Wed Nov 05 11:19:20 EST 2025</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:35:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:35:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:35:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:35:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:35:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:35:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:35:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:35:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:36:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:36:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:36:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:36:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:36:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:37:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:37:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:37:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:37:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:37:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:37:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:37:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:37:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:38:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:38:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:38:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:38:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:38:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:38:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:38:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:39:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:39:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:39:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:39:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:39:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:39:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:40:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:40:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:40:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:40:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:40:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:40:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:40:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:40:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:41:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:41:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:41:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:41:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:41:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:41:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:42:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:42:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:42:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:42:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:42:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:42:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:43:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:43:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:43:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:43:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:43:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:43:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:57:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:57:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:57:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:57:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:57:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:58:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:58:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:58:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:58:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:58:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:58:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:58:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:59:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:59:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:59:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:59:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:59:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:59:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:59:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:00:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:00:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:00:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:00:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:00:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:00:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:01:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:01:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:01:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:01:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:01:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:01:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:01:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:01:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:02:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:02:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:02:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:02:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:02:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:02:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:02:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:03:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:03:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:03:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:03:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:03:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:03:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:03:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:03:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:04:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:04:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:04:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:04:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:04:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:04:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:04:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:04:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:05:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:05:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:05:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:05:36 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -1274,7 +1634,7 @@
         <v>84</v>
       </c>
       <c r="B2" t="s">
-        <v>215</v>
+        <v>335</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>10</v>
@@ -1297,7 +1657,7 @@
         <v>84</v>
       </c>
       <c r="B3" t="s">
-        <v>216</v>
+        <v>336</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>10</v>
@@ -1320,7 +1680,7 @@
         <v>84</v>
       </c>
       <c r="B4" t="s">
-        <v>217</v>
+        <v>337</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>10</v>
@@ -1343,7 +1703,7 @@
         <v>84</v>
       </c>
       <c r="B5" t="s">
-        <v>218</v>
+        <v>338</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>10</v>
@@ -1366,7 +1726,7 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>219</v>
+        <v>339</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>10</v>
@@ -1389,7 +1749,7 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>220</v>
+        <v>340</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>10</v>
@@ -1412,7 +1772,7 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>221</v>
+        <v>341</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>10</v>
@@ -1435,7 +1795,7 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>222</v>
+        <v>342</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>10</v>
@@ -1458,7 +1818,7 @@
         <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>223</v>
+        <v>343</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>10</v>
@@ -1481,7 +1841,7 @@
         <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>224</v>
+        <v>344</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>10</v>
@@ -1504,7 +1864,7 @@
         <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>225</v>
+        <v>345</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>10</v>
@@ -1527,7 +1887,7 @@
         <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>226</v>
+        <v>346</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>10</v>
@@ -1550,7 +1910,7 @@
         <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>227</v>
+        <v>347</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>10</v>
@@ -1573,7 +1933,7 @@
         <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>228</v>
+        <v>348</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>10</v>
@@ -1596,7 +1956,7 @@
         <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>229</v>
+        <v>349</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>10</v>
@@ -1619,7 +1979,7 @@
         <v>84</v>
       </c>
       <c r="B17" t="s">
-        <v>230</v>
+        <v>350</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>10</v>
@@ -1642,7 +2002,7 @@
         <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>231</v>
+        <v>351</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>10</v>
@@ -1665,7 +2025,7 @@
         <v>84</v>
       </c>
       <c r="B19" t="s">
-        <v>232</v>
+        <v>352</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>10</v>
@@ -1688,7 +2048,7 @@
         <v>84</v>
       </c>
       <c r="B20" t="s">
-        <v>233</v>
+        <v>353</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>10</v>
@@ -1711,7 +2071,7 @@
         <v>84</v>
       </c>
       <c r="B21" t="s">
-        <v>234</v>
+        <v>354</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>10</v>
@@ -1734,7 +2094,7 @@
         <v>84</v>
       </c>
       <c r="B22" t="s">
-        <v>235</v>
+        <v>355</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>10</v>
@@ -1757,7 +2117,7 @@
         <v>84</v>
       </c>
       <c r="B23" t="s">
-        <v>236</v>
+        <v>356</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>10</v>
@@ -1780,7 +2140,7 @@
         <v>84</v>
       </c>
       <c r="B24" t="s">
-        <v>237</v>
+        <v>357</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>10</v>
@@ -1803,7 +2163,7 @@
         <v>84</v>
       </c>
       <c r="B25" t="s">
-        <v>238</v>
+        <v>358</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>10</v>
@@ -1826,7 +2186,7 @@
         <v>84</v>
       </c>
       <c r="B26" t="s">
-        <v>239</v>
+        <v>359</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>10</v>
@@ -1849,7 +2209,7 @@
         <v>84</v>
       </c>
       <c r="B27" t="s">
-        <v>240</v>
+        <v>360</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>10</v>
@@ -1872,7 +2232,7 @@
         <v>84</v>
       </c>
       <c r="B28" t="s">
-        <v>241</v>
+        <v>361</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>10</v>
@@ -1895,7 +2255,7 @@
         <v>84</v>
       </c>
       <c r="B29" t="s">
-        <v>242</v>
+        <v>362</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>10</v>
@@ -1918,7 +2278,7 @@
         <v>84</v>
       </c>
       <c r="B30" t="s">
-        <v>243</v>
+        <v>363</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>10</v>
@@ -1941,7 +2301,7 @@
         <v>84</v>
       </c>
       <c r="B31" t="s">
-        <v>244</v>
+        <v>364</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>10</v>
@@ -1964,7 +2324,7 @@
         <v>84</v>
       </c>
       <c r="B32" t="s">
-        <v>245</v>
+        <v>365</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>10</v>
@@ -1987,7 +2347,7 @@
         <v>84</v>
       </c>
       <c r="B33" t="s">
-        <v>246</v>
+        <v>366</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>10</v>
@@ -2010,7 +2370,7 @@
         <v>84</v>
       </c>
       <c r="B34" t="s">
-        <v>247</v>
+        <v>367</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>10</v>
@@ -2033,7 +2393,7 @@
         <v>84</v>
       </c>
       <c r="B35" t="s">
-        <v>248</v>
+        <v>368</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>10</v>
@@ -2056,7 +2416,7 @@
         <v>84</v>
       </c>
       <c r="B36" t="s">
-        <v>249</v>
+        <v>369</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>10</v>
@@ -2079,7 +2439,7 @@
         <v>84</v>
       </c>
       <c r="B37" t="s">
-        <v>250</v>
+        <v>370</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>10</v>
@@ -2102,7 +2462,7 @@
         <v>84</v>
       </c>
       <c r="B38" t="s">
-        <v>251</v>
+        <v>371</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>10</v>
@@ -2125,7 +2485,7 @@
         <v>84</v>
       </c>
       <c r="B39" t="s">
-        <v>252</v>
+        <v>372</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>10</v>
@@ -2148,7 +2508,7 @@
         <v>84</v>
       </c>
       <c r="B40" t="s">
-        <v>253</v>
+        <v>373</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>10</v>
@@ -2240,7 +2600,7 @@
         <v>84</v>
       </c>
       <c r="B44" t="s">
-        <v>254</v>
+        <v>374</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>10</v>
@@ -2263,7 +2623,7 @@
         <v>84</v>
       </c>
       <c r="B45" t="s">
-        <v>255</v>
+        <v>375</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>10</v>
@@ -2286,7 +2646,7 @@
         <v>84</v>
       </c>
       <c r="B46" t="s">
-        <v>256</v>
+        <v>376</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>10</v>
@@ -2309,7 +2669,7 @@
         <v>84</v>
       </c>
       <c r="B47" t="s">
-        <v>257</v>
+        <v>377</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>10</v>
@@ -2332,7 +2692,7 @@
         <v>84</v>
       </c>
       <c r="B48" t="s">
-        <v>258</v>
+        <v>378</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>10</v>
@@ -2355,7 +2715,7 @@
         <v>84</v>
       </c>
       <c r="B49" t="s">
-        <v>259</v>
+        <v>379</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>10</v>
@@ -2378,7 +2738,7 @@
         <v>84</v>
       </c>
       <c r="B50" t="s">
-        <v>260</v>
+        <v>380</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>10</v>
@@ -2401,7 +2761,7 @@
         <v>84</v>
       </c>
       <c r="B51" t="s">
-        <v>261</v>
+        <v>381</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>10</v>
@@ -2424,7 +2784,7 @@
         <v>84</v>
       </c>
       <c r="B52" t="s">
-        <v>262</v>
+        <v>382</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>10</v>
@@ -2447,7 +2807,7 @@
         <v>84</v>
       </c>
       <c r="B53" t="s">
-        <v>263</v>
+        <v>383</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>10</v>
@@ -2470,7 +2830,7 @@
         <v>84</v>
       </c>
       <c r="B54" t="s">
-        <v>264</v>
+        <v>384</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>10</v>
@@ -2493,7 +2853,7 @@
         <v>84</v>
       </c>
       <c r="B55" t="s">
-        <v>265</v>
+        <v>385</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>10</v>
@@ -2516,7 +2876,7 @@
         <v>84</v>
       </c>
       <c r="B56" t="s">
-        <v>266</v>
+        <v>386</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>10</v>
@@ -2539,7 +2899,7 @@
         <v>84</v>
       </c>
       <c r="B57" t="s">
-        <v>267</v>
+        <v>387</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>10</v>
@@ -2562,7 +2922,7 @@
         <v>84</v>
       </c>
       <c r="B58" t="s">
-        <v>268</v>
+        <v>388</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>10</v>
@@ -2654,7 +3014,7 @@
         <v>84</v>
       </c>
       <c r="B62" t="s">
-        <v>269</v>
+        <v>389</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>10</v>
@@ -2677,7 +3037,7 @@
         <v>84</v>
       </c>
       <c r="B63" t="s">
-        <v>270</v>
+        <v>390</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>10</v>
@@ -2700,7 +3060,7 @@
         <v>84</v>
       </c>
       <c r="B64" t="s">
-        <v>271</v>
+        <v>391</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>10</v>
@@ -2723,7 +3083,7 @@
         <v>84</v>
       </c>
       <c r="B65" t="s">
-        <v>272</v>
+        <v>392</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>10</v>
@@ -2746,7 +3106,7 @@
         <v>84</v>
       </c>
       <c r="B66" t="s">
-        <v>273</v>
+        <v>393</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>10</v>
@@ -2769,7 +3129,7 @@
         <v>84</v>
       </c>
       <c r="B67" t="s">
-        <v>274</v>
+        <v>394</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>10</v>

--- a/KatalonData/RADTestData/EL-NumberValidation.xlsx
+++ b/KatalonData/RADTestData/EL-NumberValidation.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{D8FBDE90-77F9-471E-A46F-C9502CC40902}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1726FB5-7E2D-4495-B7CC-32F93D9D33CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="15840" windowWidth="29040" xWindow="28680" xr2:uid="{466F649A-3E53-458C-A455-8A6BC3303076}" yWindow="-3945"/>
+    <workbookView xWindow="45972" yWindow="2952" windowWidth="30936" windowHeight="16776" xr2:uid="{466F649A-3E53-458C-A455-8A6BC3303076}"/>
   </bookViews>
   <sheets>
-    <sheet name="NumberError" r:id="rId1" sheetId="2"/>
-    <sheet name="Sheet2" r:id="rId2" sheetId="1"/>
+    <sheet name="NumberError" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1758" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="202">
   <si>
     <t>Result</t>
   </si>
@@ -300,928 +300,349 @@
     <t>PTE Composite</t>
   </si>
   <si>
-    <t>Mon Feb 24 22:38:26 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:38:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:38:47 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:38:58 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:39:08 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:39:19 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:39:29 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:39:40 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:39:51 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:40:01 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:40:11 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:40:22 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:40:32 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:40:42 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:40:52 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:41:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:41:12 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:41:23 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:41:34 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:41:44 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:41:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:42:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:42:15 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:42:25 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:42:35 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:42:45 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:42:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:43:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:43:15 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:43:26 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:43:36 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:43:49 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:43:58 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:44:10 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:44:22 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:44:32 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:44:42 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:44:52 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:45:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:45:12 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:45:24 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:45:33 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:45:43 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:45:53 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:46:03 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:46:14 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:46:23 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:46:33 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:46:43 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:46:53 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:47:03 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:47:13 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:47:23 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:47:34 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:47:44 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:47:54 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:48:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:48:15 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:48:26 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:48:40 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:48:50 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:48:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:49:09 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:49:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:49:30 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 22:49:40 EST 2025</t>
-  </si>
-  <si>
     <t>DoNotRun</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:09:19 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:09:24 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:09:29 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:09:34 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:09:39 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:09:43 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:09:48 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:09:53 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:09:58 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:10:03 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:10:07 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:10:12 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:10:16 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:10:19 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:10:23 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:10:26 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:10:30 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:10:33 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:10:36 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:10:40 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:10:43 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:10:46 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:10:50 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:10:53 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:10:56 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:11:00 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:11:03 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:11:06 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:11:11 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:11:15 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:11:18 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:11:21 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:11:24 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:11:28 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:11:31 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:11:35 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:11:38 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:11:41 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:11:45 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:11:48 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:11:51 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:11:55 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:11:58 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:12:01 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:12:05 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:12:08 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:12:12 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:12:15 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:12:18 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:12:21 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:12:25 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:12:28 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:12:32 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:12:35 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:12:39 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:12:42 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:12:45 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:12:48 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:12:52 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:12:56 EDT 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:13:51 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:14:00 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:14:07 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:14:13 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:14:19 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:14:24 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:14:31 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:14:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:14:42 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:14:47 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:14:52 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:14:57 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:15:03 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:15:08 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:15:13 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:15:18 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:15:23 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:15:29 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:15:35 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:15:40 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:15:45 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:15:51 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:15:56 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:16:03 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:16:09 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:16:15 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:16:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:16:24 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:16:30 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:16:35 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:16:40 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:16:45 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:16:51 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:16:57 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:17:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:17:07 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:17:13 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:17:19 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:17:25 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:17:30 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:17:35 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:17:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:17:47 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:17:52 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:17:57 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:18:03 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:18:08 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:18:14 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:18:19 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:18:24 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:18:31 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:18:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:18:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:18:47 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:18:53 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:18:58 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:19:03 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:19:08 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:19:14 EST 2025</t>
-  </si>
-  <si>
-    <t>Wed Nov 05 11:19:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:35:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:35:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:35:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:35:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:35:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:35:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:35:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:35:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:36:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:36:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:36:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:36:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:36:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:37:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:37:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:37:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:37:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:37:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:37:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:37:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:37:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:38:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:38:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:38:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:38:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:38:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:38:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:38:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:39:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:39:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:39:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:39:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:39:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:39:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:40:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:40:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:40:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:40:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:40:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:40:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:40:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:40:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:41:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:41:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:41:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:41:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:41:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:41:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:42:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:42:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:42:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:42:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:42:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:42:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:43:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:43:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:43:15 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:43:23 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:43:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:43:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:57:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:57:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:57:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:57:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:57:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:58:00 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:58:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:58:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:58:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:58:37 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:58:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:58:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:59:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:59:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:59:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:59:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:59:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:59:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:59:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:00:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:00:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:00:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:00:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:00:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:00:50 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:01:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:01:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:01:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:01:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:01:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:01:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:01:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:01:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:02:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:02:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:02:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:02:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:02:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:02:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:02:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:03:02 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:03:10 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:03:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:03:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:03:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:03:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:03:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:03:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:04:05 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:04:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:04:21 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:04:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:04:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:04:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:04:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:04:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:05:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:05:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:05:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:05:36 EDT 2026</t>
+    <t>Wed Jun 24 23:26:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:26:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:26:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:26:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:27:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:27:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:27:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:27:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:27:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:27:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:27:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:27:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:28:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:28:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:28:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:28:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:28:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:28:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:28:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:29:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:29:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:29:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:29:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:29:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:29:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:29:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:29:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:30:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:30:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:30:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:30:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:30:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:30:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:30:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:30:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:31:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:31:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:31:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:31:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:31:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:31:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:31:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:32:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:32:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:32:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:32:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:32:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:32:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:32:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:32:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:33:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:33:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:33:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:33:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:33:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:33:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 23:33:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:26:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:26:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:26:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:26:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:26:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:26:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:26:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:26:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:27:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:27:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:27:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:27:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:27:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:27:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:27:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:27:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:28:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:28:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:28:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:28:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:28:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:28:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:28:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:28:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:29:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:29:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:29:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:29:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:29:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:29:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:29:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:29:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:30:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:30:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:30:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:30:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:30:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:30:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:30:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:30:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:31:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:31:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:31:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:31:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:31:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:31:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:31:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:31:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:32:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:32:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:32:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:32:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:32:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:32:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:32:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:32:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 22:33:03 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -1271,20 +692,20 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1301,10 +722,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -1339,7 +760,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1391,7 +812,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1502,21 +923,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1533,7 +954,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1585,28 +1006,28 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83D66D2-4D2B-4A65-94BC-7BBA002436C7}">
-  <dimension ref="A1:H67"/>
-  <sheetFormatPr defaultColWidth="27" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83D66D2-4D2B-4A65-94BC-7BBA002436C7}">
+  <dimension ref="A1:G67"/>
+  <sheetFormatPr defaultColWidth="27" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="2" width="6.54296875" collapsed="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="2" width="6.53125" collapsed="true"/>
     <col min="2" max="2" style="2" width="27.0" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="2" width="15.26953125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="2" width="48.7265625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="40.81640625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="2" width="15.265625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="2" width="48.73046875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="40.796875" collapsed="true"/>
     <col min="6" max="6" style="2" width="27.0" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="97.26953125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="97.265625" collapsed="true"/>
     <col min="8" max="16384" style="2" width="27.0" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1629,12 +1050,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B2" t="s">
-        <v>335</v>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>10</v>
@@ -1652,12 +1073,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B3" t="s">
-        <v>336</v>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>10</v>
@@ -1675,12 +1096,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B4" t="s">
-        <v>337</v>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>10</v>
@@ -1698,12 +1119,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>84</v>
-      </c>
-      <c r="B5" t="s">
-        <v>338</v>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>148</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>10</v>
@@ -1721,12 +1142,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>84</v>
-      </c>
-      <c r="B6" t="s">
-        <v>339</v>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>149</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>10</v>
@@ -1744,12 +1165,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>84</v>
-      </c>
-      <c r="B7" t="s">
-        <v>340</v>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>10</v>
@@ -1767,12 +1188,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" t="s">
-        <v>341</v>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>151</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>10</v>
@@ -1790,12 +1211,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>84</v>
-      </c>
-      <c r="B9" t="s">
-        <v>342</v>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>152</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>10</v>
@@ -1813,12 +1234,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" t="s">
-        <v>343</v>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>153</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>10</v>
@@ -1836,12 +1257,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>84</v>
-      </c>
-      <c r="B11" t="s">
-        <v>344</v>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>154</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>10</v>
@@ -1859,12 +1280,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>84</v>
-      </c>
-      <c r="B12" t="s">
-        <v>345</v>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A12" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>10</v>
@@ -1882,12 +1303,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>84</v>
-      </c>
-      <c r="B13" t="s">
-        <v>346</v>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A13" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>10</v>
@@ -1905,12 +1326,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>84</v>
-      </c>
-      <c r="B14" t="s">
-        <v>347</v>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A14" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>157</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>10</v>
@@ -1928,12 +1349,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>84</v>
-      </c>
-      <c r="B15" t="s">
-        <v>348</v>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A15" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>158</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>10</v>
@@ -1951,12 +1372,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B16" t="s">
-        <v>349</v>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>159</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>10</v>
@@ -1974,12 +1395,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>84</v>
-      </c>
-      <c r="B17" t="s">
-        <v>350</v>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>160</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>10</v>
@@ -1997,12 +1418,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>84</v>
-      </c>
-      <c r="B18" t="s">
-        <v>351</v>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A18" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>161</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>10</v>
@@ -2020,12 +1441,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>84</v>
-      </c>
-      <c r="B19" t="s">
-        <v>352</v>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A19" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>162</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>10</v>
@@ -2043,12 +1464,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>84</v>
-      </c>
-      <c r="B20" t="s">
-        <v>353</v>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>163</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>10</v>
@@ -2066,12 +1487,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>84</v>
-      </c>
-      <c r="B21" t="s">
-        <v>354</v>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A21" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>164</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>10</v>
@@ -2089,12 +1510,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>84</v>
-      </c>
-      <c r="B22" t="s">
-        <v>355</v>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A22" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>10</v>
@@ -2112,12 +1533,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>84</v>
-      </c>
-      <c r="B23" t="s">
-        <v>356</v>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A23" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>10</v>
@@ -2135,12 +1556,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>84</v>
-      </c>
-      <c r="B24" t="s">
-        <v>357</v>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A24" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>167</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>10</v>
@@ -2158,12 +1579,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>84</v>
-      </c>
-      <c r="B25" t="s">
-        <v>358</v>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A25" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>168</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>10</v>
@@ -2181,12 +1602,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>84</v>
-      </c>
-      <c r="B26" t="s">
-        <v>359</v>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A26" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>169</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>10</v>
@@ -2204,12 +1625,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>84</v>
-      </c>
-      <c r="B27" t="s">
-        <v>360</v>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A27" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>170</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>10</v>
@@ -2227,12 +1648,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>84</v>
-      </c>
-      <c r="B28" t="s">
-        <v>361</v>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A28" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>10</v>
@@ -2250,12 +1671,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>84</v>
-      </c>
-      <c r="B29" t="s">
-        <v>362</v>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A29" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>10</v>
@@ -2273,12 +1694,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>84</v>
-      </c>
-      <c r="B30" t="s">
-        <v>363</v>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A30" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>10</v>
@@ -2296,12 +1717,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>84</v>
-      </c>
-      <c r="B31" t="s">
-        <v>364</v>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A31" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>10</v>
@@ -2319,12 +1740,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>84</v>
-      </c>
-      <c r="B32" t="s">
-        <v>365</v>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A32" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>175</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>10</v>
@@ -2342,12 +1763,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>84</v>
-      </c>
-      <c r="B33" t="s">
-        <v>366</v>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A33" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>176</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>10</v>
@@ -2365,12 +1786,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>84</v>
-      </c>
-      <c r="B34" t="s">
-        <v>367</v>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A34" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>177</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>10</v>
@@ -2388,12 +1809,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>84</v>
-      </c>
-      <c r="B35" t="s">
-        <v>368</v>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A35" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>178</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>10</v>
@@ -2411,12 +1832,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>84</v>
-      </c>
-      <c r="B36" t="s">
-        <v>369</v>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A36" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>10</v>
@@ -2434,12 +1855,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>84</v>
-      </c>
-      <c r="B37" t="s">
-        <v>370</v>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A37" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>180</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>10</v>
@@ -2457,12 +1878,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>84</v>
-      </c>
-      <c r="B38" t="s">
-        <v>371</v>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A38" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>181</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>10</v>
@@ -2480,12 +1901,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>84</v>
-      </c>
-      <c r="B39" t="s">
-        <v>372</v>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A39" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>182</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>10</v>
@@ -2503,12 +1924,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>84</v>
-      </c>
-      <c r="B40" t="s">
-        <v>373</v>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A40" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>183</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>10</v>
@@ -2526,15 +1947,9 @@
         <v>83</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>84</v>
-      </c>
-      <c r="B41" t="s">
-        <v>126</v>
-      </c>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="C41" s="2" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>36</v>
@@ -2549,15 +1964,9 @@
         <v>83</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>84</v>
-      </c>
-      <c r="B42" t="s">
-        <v>127</v>
-      </c>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="C42" s="2" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>36</v>
@@ -2572,15 +1981,9 @@
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>84</v>
-      </c>
-      <c r="B43" t="s">
-        <v>128</v>
-      </c>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="C43" s="2" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>36</v>
@@ -2595,12 +1998,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>84</v>
-      </c>
-      <c r="B44" t="s">
-        <v>374</v>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A44" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>10</v>
@@ -2618,12 +2021,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>84</v>
-      </c>
-      <c r="B45" t="s">
-        <v>375</v>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A45" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>10</v>
@@ -2641,12 +2044,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>84</v>
-      </c>
-      <c r="B46" t="s">
-        <v>376</v>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A46" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>186</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>10</v>
@@ -2664,12 +2067,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>84</v>
-      </c>
-      <c r="B47" t="s">
-        <v>377</v>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A47" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>187</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>10</v>
@@ -2687,12 +2090,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>84</v>
-      </c>
-      <c r="B48" t="s">
-        <v>378</v>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A48" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>188</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>10</v>
@@ -2710,12 +2113,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>84</v>
-      </c>
-      <c r="B49" t="s">
-        <v>379</v>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A49" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>189</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>10</v>
@@ -2733,12 +2136,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>84</v>
-      </c>
-      <c r="B50" t="s">
-        <v>380</v>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A50" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>190</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>10</v>
@@ -2756,12 +2159,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>84</v>
-      </c>
-      <c r="B51" t="s">
-        <v>381</v>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A51" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>191</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>10</v>
@@ -2779,12 +2182,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>84</v>
-      </c>
-      <c r="B52" t="s">
-        <v>382</v>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A52" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>192</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>10</v>
@@ -2802,12 +2205,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>84</v>
-      </c>
-      <c r="B53" t="s">
-        <v>383</v>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A53" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>193</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>10</v>
@@ -2825,12 +2228,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>84</v>
-      </c>
-      <c r="B54" t="s">
-        <v>384</v>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A54" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>194</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>10</v>
@@ -2848,12 +2251,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>84</v>
-      </c>
-      <c r="B55" t="s">
-        <v>385</v>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A55" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>195</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>10</v>
@@ -2871,12 +2274,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>84</v>
-      </c>
-      <c r="B56" t="s">
-        <v>386</v>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A56" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>196</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>10</v>
@@ -2894,12 +2297,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>84</v>
-      </c>
-      <c r="B57" t="s">
-        <v>387</v>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A57" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>197</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>10</v>
@@ -2917,12 +2320,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>84</v>
-      </c>
-      <c r="B58" t="s">
-        <v>388</v>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A58" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>198</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>10</v>
@@ -2940,15 +2343,9 @@
         <v>83</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>84</v>
-      </c>
-      <c r="B59" t="s">
-        <v>144</v>
-      </c>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="C59" s="2" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>36</v>
@@ -2963,15 +2360,9 @@
         <v>83</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>84</v>
-      </c>
-      <c r="B60" t="s">
-        <v>145</v>
-      </c>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="C60" s="2" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>36</v>
@@ -2986,15 +2377,9 @@
         <v>83</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>84</v>
-      </c>
-      <c r="B61" t="s">
-        <v>146</v>
-      </c>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="C61" s="2" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>36</v>
@@ -3009,12 +2394,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>84</v>
-      </c>
-      <c r="B62" t="s">
-        <v>389</v>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A62" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>199</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>10</v>
@@ -3032,12 +2417,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>84</v>
-      </c>
-      <c r="B63" t="s">
-        <v>390</v>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A63" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>200</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>10</v>
@@ -3055,12 +2440,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>84</v>
-      </c>
-      <c r="B64" t="s">
-        <v>391</v>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A64" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>201</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>10</v>
@@ -3078,15 +2463,9 @@
         <v>83</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>84</v>
-      </c>
-      <c r="B65" t="s">
-        <v>392</v>
-      </c>
+    <row r="65" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C65" s="2" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>36</v>
@@ -3101,15 +2480,9 @@
         <v>83</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>84</v>
-      </c>
-      <c r="B66" t="s">
-        <v>393</v>
-      </c>
+    <row r="66" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C66" s="2" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>36</v>
@@ -3124,15 +2497,9 @@
         <v>83</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>84</v>
-      </c>
-      <c r="B67" t="s">
-        <v>394</v>
-      </c>
+    <row r="67" spans="3:7" x14ac:dyDescent="0.45">
       <c r="C67" s="2" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>36</v>
@@ -3148,27 +2515,27 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6057E2E3-7C58-4120-B02D-BA3B396B9DA0}">
-  <dimension ref="A1:H47"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6057E2E3-7C58-4120-B02D-BA3B396B9DA0}">
+  <dimension ref="A1:G47"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="2" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.81640625" collapsed="true"/>
-    <col min="3" max="3" style="2" width="9.1796875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="2" width="48.1796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="2" width="53.54296875" collapsed="true"/>
+    <col min="1" max="1" style="2" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="2" width="27.796875" collapsed="true"/>
+    <col min="3" max="3" style="2" width="9.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="2" width="48.19921875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="53.53125" collapsed="true"/>
     <col min="6" max="6" customWidth="true" style="2" width="26.0" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="2" width="80.54296875" collapsed="true"/>
-    <col min="8" max="16384" style="2" width="9.1796875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="2" width="80.53125" collapsed="true"/>
+    <col min="8" max="16384" style="2" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3191,11 +2558,11 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -3214,11 +2581,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -3237,11 +2604,11 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -3260,11 +2627,11 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -3283,11 +2650,11 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -3306,11 +2673,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -3329,11 +2696,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -3352,11 +2719,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" t="s">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -3375,11 +2742,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -3398,11 +2765,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -3421,11 +2788,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>47</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -3444,11 +2811,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -3467,11 +2834,11 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -3490,11 +2857,11 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -3513,11 +2880,11 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -3536,11 +2903,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" t="s">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -3559,11 +2926,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" t="s">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -3582,11 +2949,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" t="s">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -3605,11 +2972,11 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" t="s">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -3628,11 +2995,11 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" t="s">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -3651,11 +3018,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" t="s">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C22" s="1" t="s">
@@ -3674,11 +3041,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" t="s">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C23" s="1" t="s">
@@ -3697,11 +3064,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" t="s">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -3720,11 +3087,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25" t="s">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A25" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -3743,11 +3110,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" t="s">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A26" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -3766,11 +3133,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" t="s">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -3789,11 +3156,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" t="s">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C28" s="1" t="s">
@@ -3812,11 +3179,11 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" t="s">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -3835,11 +3202,11 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>35</v>
-      </c>
-      <c r="B30" t="s">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C30" s="1" t="s">
@@ -3858,11 +3225,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" t="s">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A31" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C31" s="1" t="s">
@@ -3881,11 +3248,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A32" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C32" s="1" t="s">
@@ -3904,11 +3271,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" t="s">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A33" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>68</v>
       </c>
       <c r="C33" s="1" t="s">
@@ -3927,11 +3294,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" t="s">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A34" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -3950,11 +3317,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35" t="s">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A35" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C35" s="1" t="s">
@@ -3973,11 +3340,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A36" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C36" s="1" t="s">
@@ -3996,11 +3363,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" t="s">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A37" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C37" s="1" t="s">
@@ -4019,11 +3386,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>35</v>
-      </c>
-      <c r="B38" t="s">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A38" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C38" s="1" t="s">
@@ -4042,11 +3409,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>35</v>
-      </c>
-      <c r="B39" t="s">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A39" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C39" s="1" t="s">
@@ -4065,11 +3432,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>35</v>
-      </c>
-      <c r="B40" t="s">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A40" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C40" s="1" t="s">
@@ -4088,11 +3455,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>35</v>
-      </c>
-      <c r="B41" t="s">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A41" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C41" s="1" t="s">
@@ -4111,11 +3478,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>35</v>
-      </c>
-      <c r="B42" t="s">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A42" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C42" s="1" t="s">
@@ -4134,11 +3501,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>35</v>
-      </c>
-      <c r="B43" t="s">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A43" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C43" s="1" t="s">
@@ -4157,11 +3524,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>35</v>
-      </c>
-      <c r="B44" t="s">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C44" s="1" t="s">
@@ -4180,11 +3547,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>35</v>
-      </c>
-      <c r="B45" t="s">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A45" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C45" s="1" t="s">
@@ -4203,11 +3570,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>35</v>
-      </c>
-      <c r="B46" t="s">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A46" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C46" s="1" t="s">
@@ -4226,11 +3593,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>35</v>
-      </c>
-      <c r="B47" t="s">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A47" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C47" s="1" t="s">
@@ -4250,8 +3617,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
